--- a/output/2026-09-02_13_Italia_Abruzzo_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-02_13_Italia_Abruzzo_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ferramenta/utensileria/forniture industriali e DPI per professionisti e imprese, Bazzano; esistenza confermata via ricerca web (Atoka, sito ufficiale, PagineSI)</t>
+          <t>Ferramenta/utensileria/forniture industriali e DPI per professionisti e imprese, Bazzano; esistenza confermata via ricerca web (Atoka, sito ufficiale, PagineSI) [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ferramenta, utensileria, forniture industriali e bulloneria, Avezzano; confermata via sito ufficiale e PagineGialle</t>
+          <t>Ferramenta, utensileria, forniture industriali e bulloneria, Avezzano; confermata via sito ufficiale e PagineGialle [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -562,7 +562,6 @@
           <t>Utensileria Abruzzese 94 S.r.l.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>L'Aquila (AQ)</t>
@@ -578,7 +577,6 @@
           <t>0863 412567</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Grossista utensili manuali/elettrici e ferramenta per industria, Avezzano; confermata via Kompass/PagineGialle; nessun sito web reperito, email non verificabile</t>
@@ -616,10 +614,9 @@
           <t>0863 22720 / 0863 26894</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distribuzione articoli industriali/forniture per manutenzione, cuscinetti, cinghie, Avezzano (Via Garibaldi 202); confermata multi-fonte; email non verificabile. NOTA: gruppo familiare correlato a Capassi Meccanica Industriale Srl (sede e attivita' diverse)</t>
+          <t>Distribuzione articoli industriali/forniture per manutenzione, cuscinetti, cinghie, Avezzano (Via Garibaldi 202); confermata multi-fonte; email non verificabile. NOTA: gruppo familiare correlato a Capassi Meccanica Industriale Srl (sede e attivita' diverse) [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,7 +631,6 @@
           <t>Capassi Meccanica Industriale S.r.l.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>L'Aquila (AQ)</t>
@@ -650,7 +646,6 @@
           <t>0863 509407 / 0863 509417</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Commercializzazione ingranaggi, pulegge, cuscinetti, riduttori, bulloneria, raccorderia idropneumatica, Avezzano (Via Copernico 2); confermata via PagineBianche/Reportaziende. NOTA: entita' distinta ma correlata a Capassi Paolo &amp; C. Sas (Capassi Group)</t>
@@ -695,7 +690,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Forniture industriali, macchine utensili, organi di trasmissione, rivenditore Bosch Professional, Teramo (Via Di Vittorio). P.IVA 01714980677. NOTA: gruppo correlato a Di Emidio Srl (Giulianova), entita' legale distinta</t>
+          <t>Forniture industriali, macchine utensili, organi di trasmissione, rivenditore Bosch Professional, Teramo (Via Di Vittorio). P.IVA 01714980677. NOTA: gruppo correlato a Di Emidio Srl (Giulianova), entita' legale distinta [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -772,10 +767,9 @@
           <t>085 8000096 / 085 8008850</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ricambi industriali, utensili, rivenditore Telwin (saldatura), Giulianova; confermata via sito ufficiale/PagineGialle. NOTA: telefono verificato appartenente a QUESTA azienda (non a Klinsystem, che nella lista grezza condivideva erroneamente lo stesso numero: numero reale di Klinsystem e' 085 7880800)</t>
+          <t>Ricambi industriali, utensili, rivenditore Telwin (saldatura), Giulianova; confermata via sito ufficiale/PagineGialle. NOTA: telefono verificato appartenente a QUESTA azienda (non a Klinsystem, che nella lista grezza condivideva erroneamente lo stesso numero: numero reale di Klinsystem e' 085 7880800) [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -810,10 +804,9 @@
           <t>0861 570541</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cuscinetti (distributore SKF/FAG/TIMKEN), oleodinamica, pneumatica, compressori, utensileria da taglio, Castellalto; confermata via Atoka/sito ufficiale; email non verificabile</t>
+          <t>Cuscinetti (distributore SKF/FAG/TIMKEN), oleodinamica, pneumatica, compressori, utensileria da taglio, Castellalto; confermata via Atoka/sito ufficiale; email non verificabile [DUPLICATO — vedi anche: 2026-09-02_03_Italia_Abruzzo_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -855,7 +848,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Compressori, aspiratori industriali, utensili elettrici, macchine industriali, Teramo (San Nicolo' a Tordino); confermata via sito ufficiale</t>
+          <t>Compressori, aspiratori industriali, utensili elettrici, macchine industriali, Teramo (San Nicolo' a Tordino); confermata via sito ufficiale [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -890,7 +883,6 @@
           <t>0861 743511</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Commercio macchine utensili per lavorazione metalli; unita' locale confermata a Colonnella (TE), sede legale principale a San Benedetto del Tronto (Marche/AP); email non verificata in questa ricerca</t>
@@ -935,7 +927,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Forniture tecniche industriali: pneumatica, oleodinamica, trasmissioni, cuscinetti, automazione, Martinsicuro; confermata via Atoka/sito ufficiale</t>
+          <t>Forniture tecniche industriali: pneumatica, oleodinamica, trasmissioni, cuscinetti, automazione, Martinsicuro; confermata via Atoka/sito ufficiale [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -950,7 +942,6 @@
           <t>Co.Medil S.r.l.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Teramo (TE)</t>
@@ -966,7 +957,6 @@
           <t>0861 82325</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Ferramenta industriale e distribuzione prodotti metallici, Nereto; confermata via Virgilio/Europages. NOTA: opera anche nel settore edilizia/inerti, verificare focus specifico prima di contatto commerciale; email non verificabile</t>
@@ -1011,7 +1001,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Forniture industriali: pneumatica/oleodinamica, cinghie, utensileria, aspiratori (Pneumax, Atlas Copco, Bosch Rexroth, SKF), Montesilvano; confermata via sito ufficiale/Europages</t>
+          <t>Forniture industriali: pneumatica/oleodinamica, cinghie, utensileria, aspiratori (Pneumax, Atlas Copco, Bosch Rexroth, SKF), Montesilvano; confermata via sito ufficiale/Europages [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1046,7 +1036,6 @@
           <t>085 4453749</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Commercio all'ingrosso di macchine utensili e utensileria per asportazione truciolo, Montesilvano; confermata via Atoka/Kompass; telefono reperito tramite ricerca (assente nella lista grezza); email non verificabile</t>
@@ -1084,7 +1073,6 @@
           <t>085 4710291</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Vendita e assistenza compressori d'aria, essiccatori, filtri, ricambi; assistenza autorizzata FINI e NUOVA DARI, Montesilvano; confermata via sito ufficiale/PagineGialle; email non verificabile</t>
@@ -1122,10 +1110,9 @@
           <t>0873 37111</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Macchine utensili, saldatrici, elettrovalvole, torni, frese, robot, centri di lavoro, Vasto; azienda dal 1978, confermata multi-fonte; email non verificabile</t>
+          <t>Macchine utensili, saldatrici, elettrovalvole, torni, frese, robot, centri di lavoro, Vasto; azienda dal 1978, confermata multi-fonte; email non verificabile [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1167,7 +1154,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Forniture industriali, oleodinamica, cuscinetti, assemblaggio tubi oleodinamici, Vasto e San Salvo; confermata via sito ufficiale, 25 anni di attivita'</t>
+          <t>Forniture industriali, oleodinamica, cuscinetti, assemblaggio tubi oleodinamici, Vasto e San Salvo; confermata via sito ufficiale, 25 anni di attivita' [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1209,7 +1196,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Forniture industriali, oleodinamica, cuscinetteria, utensileria industriale, ferramenta, DPI, Atessa; confermata via sito ufficiale</t>
+          <t>Forniture industriali, oleodinamica, cuscinetteria, utensileria industriale, ferramenta, DPI, Atessa; confermata via sito ufficiale [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1286,7 +1273,6 @@
           <t>085 9062870</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Gas tecnici (ossigeno, argon, azoto, CO2), saldatrici, accessori TIG/MIG/plasma, impianti gas compressi; partner di industrie meccaniche in Abruzzo/Molise/Marche, Ortona; confermata via sito ufficiale; email non verificabile</t>
@@ -1324,10 +1310,9 @@
           <t>0871 561812</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Forniture industriali: cuscinetti, macchine utensili, oleodinamica/pneumatica, trasmissioni, DPI, arredamento industriale, centro assemblaggio tubi idraulici, certificata ISO 9001:2015; sede a Chieti Scalo (CH), opera sui mercati Chieti-Pescara. NOTA: nella lista grezza era stata classificata sotto Pescara ma la sede legale/operativa e' in provincia di Chieti; email non verificabile</t>
+          <t>Forniture industriali: cuscinetti, macchine utensili, oleodinamica/pneumatica, trasmissioni, DPI, arredamento industriale, centro assemblaggio tubi idraulici, certificata ISO 9001:2015; sede a Chieti Scalo (CH), opera sui mercati Chieti-Pescara. NOTA: nella lista grezza era stata classificata sotto Pescara ma la sede legale/operativa e' in provincia di Chieti; email non verificabile [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
